--- a/docs/上线/上线工作.xlsx
+++ b/docs/上线/上线工作.xlsx
@@ -8,24 +8,33 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\lyh\AI\SnapRep\docs\上线\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBC8BCA4-036C-43BE-AF09-589E2B415710}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0C41640-682F-41FB-97FF-567A936C6BEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -144,6 +153,10 @@
 动作侧：
 在“标准动作模板”的基础上，扩充到你希望 v1.0 的目标数量
 至少保证：各核心场景下不会出现「推荐不到动作」的情况</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>只是完成了基本页面，和全部页面还是差太多。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -558,7 +571,9 @@
       <c r="E3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="4"/>
+      <c r="F3" s="4" t="s">
+        <v>19</v>
+      </c>
       <c r="G3" s="2"/>
     </row>
     <row r="4" spans="2:7" ht="152.65" x14ac:dyDescent="0.4">

--- a/docs/上线/上线工作.xlsx
+++ b/docs/上线/上线工作.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\lyh\AI\SnapRep\docs\上线\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0C41640-682F-41FB-97FF-567A936C6BEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E7F8F32-F91C-4067-916F-9BB2432F91BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -157,6 +157,18 @@
   </si>
   <si>
     <t>只是完成了基本页面，和全部页面还是差太多。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>完成了皮毛，都没有经过测试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>没有开发</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>已经22号了，但是目前进度堪忧，我感觉是没有合理安排好时间和进度。应该说是对目前所处的产品的情况分不清楚。就是现实和目标的差距。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -589,7 +601,9 @@
       <c r="E4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="4"/>
+      <c r="F4" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="G4" s="2"/>
     </row>
     <row r="5" spans="2:7" ht="69.400000000000006" x14ac:dyDescent="0.4">
@@ -605,7 +619,9 @@
       <c r="E5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="4"/>
+      <c r="F5" s="4" t="s">
+        <v>21</v>
+      </c>
       <c r="G5" s="2"/>
     </row>
     <row r="6" spans="2:7" ht="124.9" x14ac:dyDescent="0.4">
@@ -624,7 +640,7 @@
       <c r="F6" s="4"/>
       <c r="G6" s="2"/>
     </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:7" ht="41.65" x14ac:dyDescent="0.4">
       <c r="B7" s="3">
         <v>45984</v>
       </c>
@@ -633,7 +649,9 @@
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
+      <c r="F7" s="4" t="s">
+        <v>22</v>
+      </c>
       <c r="G7" s="2"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.4">
